--- a/cds_files/UCF_CDS_2024-2025.xlsx
+++ b/cds_files/UCF_CDS_2024-2025.xlsx
@@ -499,7 +499,7 @@
         <v>0.68</v>
       </c>
       <c r="C3" t="n">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="4">
@@ -512,7 +512,7 @@
         <v>0.32</v>
       </c>
       <c r="C4" t="n">
-        <v>0.88</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="5">
@@ -525,7 +525,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.067</v>
       </c>
     </row>
   </sheetData>
